--- a/data/master/yeoyuro_seoul_vector_map_coordinate_workbook.xlsx
+++ b/data/master/yeoyuro_seoul_vector_map_coordinate_workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\MyProject\yeoyuro_seoul_project\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBACAB1-F6ED-4DD3-8504-2A4CAF380076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38536995-ADE5-4424-96BE-58A69D2D2B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3817,7 +3817,14 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -13188,14 +13195,14 @@
         <v>663</v>
       </c>
       <c r="I6" s="22">
-        <v>2240</v>
+        <v>2206</v>
       </c>
       <c r="J6" s="22">
         <v>980</v>
       </c>
       <c r="K6" s="23">
         <f t="shared" si="0"/>
-        <v>43.75</v>
+        <v>43.0859375</v>
       </c>
       <c r="L6" s="23">
         <f t="shared" si="1"/>
@@ -13676,14 +13683,14 @@
         <v>663</v>
       </c>
       <c r="I15" s="22">
-        <v>2200</v>
+        <v>2206</v>
       </c>
       <c r="J15" s="22">
         <v>1144</v>
       </c>
       <c r="K15" s="23">
         <f t="shared" si="0"/>
-        <v>42.96875</v>
+        <v>43.0859375</v>
       </c>
       <c r="L15" s="23">
         <f t="shared" si="1"/>
@@ -13948,18 +13955,18 @@
         <v>663</v>
       </c>
       <c r="I20" s="22">
-        <v>2864</v>
+        <v>2816</v>
       </c>
       <c r="J20" s="22">
-        <v>1188</v>
+        <v>1194</v>
       </c>
       <c r="K20" s="23">
         <f t="shared" si="0"/>
-        <v>55.937499999999993</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="L20" s="23">
         <f t="shared" si="1"/>
-        <v>41.25</v>
+        <v>41.458333333333336</v>
       </c>
       <c r="M20" s="2">
         <v>10</v>
@@ -14002,14 +14009,14 @@
         <v>663</v>
       </c>
       <c r="I21" s="22">
-        <v>2920</v>
+        <v>2896</v>
       </c>
       <c r="J21" s="22">
         <v>1244</v>
       </c>
       <c r="K21" s="23">
         <f t="shared" si="0"/>
-        <v>57.03125</v>
+        <v>56.562500000000007</v>
       </c>
       <c r="L21" s="23">
         <f t="shared" si="1"/>
@@ -20876,14 +20883,14 @@
         <v>894</v>
       </c>
       <c r="I148" s="22">
-        <v>2200</v>
+        <v>2206</v>
       </c>
       <c r="J148" s="22">
         <v>1144</v>
       </c>
       <c r="K148" s="23">
         <f t="shared" si="4"/>
-        <v>42.96875</v>
+        <v>43.0859375</v>
       </c>
       <c r="L148" s="23">
         <f t="shared" si="5"/>
@@ -27856,14 +27863,14 @@
         <v>663</v>
       </c>
       <c r="I277" s="22">
-        <v>3580</v>
+        <v>3628</v>
       </c>
       <c r="J277" s="22">
         <v>2652</v>
       </c>
       <c r="K277" s="23">
         <f t="shared" si="8"/>
-        <v>69.921875</v>
+        <v>70.859375</v>
       </c>
       <c r="L277" s="23">
         <f t="shared" si="9"/>
@@ -27910,14 +27917,14 @@
         <v>663</v>
       </c>
       <c r="I278" s="22">
-        <v>3392</v>
+        <v>3480</v>
       </c>
       <c r="J278" s="22">
         <v>2652</v>
       </c>
       <c r="K278" s="23">
         <f t="shared" si="8"/>
-        <v>66.25</v>
+        <v>67.96875</v>
       </c>
       <c r="L278" s="23">
         <f t="shared" si="9"/>
@@ -29672,14 +29679,14 @@
         <v>663</v>
       </c>
       <c r="I310" s="22">
-        <v>3112</v>
+        <v>3130</v>
       </c>
       <c r="J310" s="22">
         <v>2116</v>
       </c>
       <c r="K310" s="23">
         <f t="shared" si="8"/>
-        <v>60.78125</v>
+        <v>61.1328125</v>
       </c>
       <c r="L310" s="23">
         <f t="shared" si="9"/>
@@ -29726,14 +29733,14 @@
         <v>663</v>
       </c>
       <c r="I311" s="22">
-        <v>3112</v>
+        <v>3130</v>
       </c>
       <c r="J311" s="22">
         <v>1964</v>
       </c>
       <c r="K311" s="23">
         <f t="shared" si="8"/>
-        <v>60.78125</v>
+        <v>61.1328125</v>
       </c>
       <c r="L311" s="23">
         <f t="shared" si="9"/>
@@ -30034,11 +30041,12 @@
   <autoFilter ref="A1:R316" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A2:R316">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>COUNTIFS($I$2:$I$316,$I2,$J$2:$J$316,$J2,$D$2:$D$316,"&lt;&gt;"&amp;$D2)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -40636,16 +40644,14 @@
         <v>28</v>
       </c>
       <c r="F6" s="23">
-        <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B6,Station_Visual_Nodes!$I$2:$I$2000)+N6,0)</f>
-        <v>2240</v>
+        <v>2206</v>
       </c>
       <c r="G6" s="23">
-        <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B6,Station_Visual_Nodes!$J$2:$J$2000)+O6,0)</f>
         <v>980</v>
       </c>
       <c r="H6" s="23">
         <f t="shared" si="0"/>
-        <v>43.75</v>
+        <v>43.0859375</v>
       </c>
       <c r="I6" s="23">
         <f t="shared" si="1"/>
@@ -41029,7 +41035,7 @@
       </c>
       <c r="F14" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B14,Station_Visual_Nodes!$I$2:$I$2000)+N14,0)</f>
-        <v>2200</v>
+        <v>2206</v>
       </c>
       <c r="G14" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B14,Station_Visual_Nodes!$J$2:$J$2000)+O14,0)</f>
@@ -41037,7 +41043,7 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="0"/>
-        <v>42.96875</v>
+        <v>43.0859375</v>
       </c>
       <c r="I14" s="23">
         <f t="shared" si="1"/>
@@ -41273,20 +41279,18 @@
         <v>48</v>
       </c>
       <c r="F19" s="23">
-        <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B19,Station_Visual_Nodes!$I$2:$I$2000)+N19,0)</f>
-        <v>2864</v>
+        <v>2816</v>
       </c>
       <c r="G19" s="23">
-        <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B19,Station_Visual_Nodes!$J$2:$J$2000)+O19,0)</f>
-        <v>1188</v>
+        <v>1194</v>
       </c>
       <c r="H19" s="23">
         <f t="shared" si="0"/>
-        <v>55.937499999999993</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="I19" s="23">
         <f t="shared" si="1"/>
-        <v>41.25</v>
+        <v>41.458333333333336</v>
       </c>
       <c r="J19" s="2">
         <v>24</v>
@@ -41322,16 +41326,14 @@
         <v>48</v>
       </c>
       <c r="F20" s="23">
-        <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B20,Station_Visual_Nodes!$I$2:$I$2000)+N20,0)</f>
-        <v>2920</v>
+        <v>2896</v>
       </c>
       <c r="G20" s="23">
-        <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B20,Station_Visual_Nodes!$J$2:$J$2000)+O20,0)</f>
         <v>1244</v>
       </c>
       <c r="H20" s="23">
         <f t="shared" si="0"/>
-        <v>57.03125</v>
+        <v>56.562500000000007</v>
       </c>
       <c r="I20" s="23">
         <f t="shared" si="1"/>
@@ -51606,16 +51608,14 @@
         <v>512</v>
       </c>
       <c r="F230" s="23">
-        <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B230,Station_Visual_Nodes!$I$2:$I$2000)+N230,0)</f>
-        <v>3121</v>
+        <v>3130</v>
       </c>
       <c r="G230" s="23">
-        <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B230,Station_Visual_Nodes!$J$2:$J$2000)+O230,0)</f>
         <v>1964</v>
       </c>
       <c r="H230" s="23">
         <f t="shared" si="6"/>
-        <v>60.957031250000007</v>
+        <v>61.1328125</v>
       </c>
       <c r="I230" s="23">
         <f t="shared" si="7"/>
@@ -52097,7 +52097,7 @@
       </c>
       <c r="F240" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B240,Station_Visual_Nodes!$I$2:$I$2000)+N240,0)</f>
-        <v>3580</v>
+        <v>3628</v>
       </c>
       <c r="G240" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B240,Station_Visual_Nodes!$J$2:$J$2000)+O240,0)</f>
@@ -52105,7 +52105,7 @@
       </c>
       <c r="H240" s="23">
         <f t="shared" si="6"/>
-        <v>69.921875</v>
+        <v>70.859375</v>
       </c>
       <c r="I240" s="23">
         <f t="shared" si="7"/>
@@ -52146,7 +52146,7 @@
       </c>
       <c r="F241" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B241,Station_Visual_Nodes!$I$2:$I$2000)+N241,0)</f>
-        <v>3392</v>
+        <v>3480</v>
       </c>
       <c r="G241" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B241,Station_Visual_Nodes!$J$2:$J$2000)+O241,0)</f>
@@ -52154,7 +52154,7 @@
       </c>
       <c r="H241" s="23">
         <f t="shared" si="6"/>
-        <v>66.25</v>
+        <v>67.96875</v>
       </c>
       <c r="I241" s="23">
         <f t="shared" si="7"/>
@@ -53369,14 +53369,14 @@
         <v>537</v>
       </c>
       <c r="F267" s="23">
-        <v>3112</v>
+        <v>3130</v>
       </c>
       <c r="G267" s="23">
         <v>2116</v>
       </c>
       <c r="H267" s="23">
         <f t="shared" si="8"/>
-        <v>60.78125</v>
+        <v>61.1328125</v>
       </c>
       <c r="I267" s="23">
         <f t="shared" si="9"/>
@@ -53902,8 +53902,7 @@
         <v>28</v>
       </c>
       <c r="F6" s="23">
-        <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B6,Station_Visual_Nodes!$I$2:$I$2000)+P6,0)</f>
-        <v>2240</v>
+        <v>2206</v>
       </c>
       <c r="G6" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B6,Station_Visual_Nodes!$J$2:$J$2000)+Q6,0)</f>
@@ -53911,7 +53910,7 @@
       </c>
       <c r="H6" s="23">
         <f t="shared" si="0"/>
-        <v>43.75</v>
+        <v>43.0859375</v>
       </c>
       <c r="I6" s="23">
         <f t="shared" si="1"/>
@@ -54343,7 +54342,7 @@
       </c>
       <c r="F14" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B14,Station_Visual_Nodes!$I$2:$I$2000)+P14,0)</f>
-        <v>2200</v>
+        <v>2206</v>
       </c>
       <c r="G14" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B14,Station_Visual_Nodes!$J$2:$J$2000)+Q14,0)</f>
@@ -54351,7 +54350,7 @@
       </c>
       <c r="H14" s="23">
         <f t="shared" si="0"/>
-        <v>42.96875</v>
+        <v>43.0859375</v>
       </c>
       <c r="I14" s="23">
         <f t="shared" si="1"/>
@@ -54617,20 +54616,18 @@
         <v>48</v>
       </c>
       <c r="F19" s="23">
-        <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B19,Station_Visual_Nodes!$I$2:$I$2000)+P19,0)</f>
-        <v>2864</v>
+        <v>2816</v>
       </c>
       <c r="G19" s="23">
-        <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B19,Station_Visual_Nodes!$J$2:$J$2000)+Q19,0)</f>
-        <v>1188</v>
+        <v>1194</v>
       </c>
       <c r="H19" s="23">
         <f t="shared" si="0"/>
-        <v>55.937499999999993</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="I19" s="23">
         <f t="shared" si="1"/>
-        <v>41.25</v>
+        <v>41.458333333333336</v>
       </c>
       <c r="J19" s="2">
         <v>10.5</v>
@@ -54672,16 +54669,14 @@
         <v>48</v>
       </c>
       <c r="F20" s="23">
-        <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B20,Station_Visual_Nodes!$I$2:$I$2000)+P20,0)</f>
-        <v>2920</v>
+        <v>2896</v>
       </c>
       <c r="G20" s="23">
-        <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B20,Station_Visual_Nodes!$J$2:$J$2000)+Q20,0)</f>
         <v>1244</v>
       </c>
       <c r="H20" s="23">
         <f t="shared" si="0"/>
-        <v>57.03125</v>
+        <v>56.562500000000007</v>
       </c>
       <c r="I20" s="23">
         <f t="shared" si="1"/>
@@ -66222,7 +66217,7 @@
       </c>
       <c r="F230" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B230,Station_Visual_Nodes!$I$2:$I$2000)+P230,0)</f>
-        <v>3121</v>
+        <v>3130</v>
       </c>
       <c r="G230" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B230,Station_Visual_Nodes!$J$2:$J$2000)+Q230,0)</f>
@@ -66230,7 +66225,7 @@
       </c>
       <c r="H230" s="23">
         <f t="shared" si="6"/>
-        <v>60.957031250000007</v>
+        <v>61.1328125</v>
       </c>
       <c r="I230" s="23">
         <f t="shared" si="7"/>
@@ -66772,7 +66767,7 @@
       </c>
       <c r="F240" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B240,Station_Visual_Nodes!$I$2:$I$2000)+P240,0)</f>
-        <v>3580</v>
+        <v>3628</v>
       </c>
       <c r="G240" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B240,Station_Visual_Nodes!$J$2:$J$2000)+Q240,0)</f>
@@ -66780,7 +66775,7 @@
       </c>
       <c r="H240" s="23">
         <f t="shared" si="6"/>
-        <v>69.921875</v>
+        <v>70.859375</v>
       </c>
       <c r="I240" s="23">
         <f t="shared" si="7"/>
@@ -66827,7 +66822,7 @@
       </c>
       <c r="F241" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B241,Station_Visual_Nodes!$I$2:$I$2000)+P241,0)</f>
-        <v>3392</v>
+        <v>3480</v>
       </c>
       <c r="G241" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B241,Station_Visual_Nodes!$J$2:$J$2000)+Q241,0)</f>
@@ -66835,7 +66830,7 @@
       </c>
       <c r="H241" s="23">
         <f t="shared" si="6"/>
-        <v>66.25</v>
+        <v>67.96875</v>
       </c>
       <c r="I241" s="23">
         <f t="shared" si="7"/>
@@ -68249,7 +68244,7 @@
       </c>
       <c r="F267" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B267,Station_Visual_Nodes!$I$2:$I$2000)+P267,0)</f>
-        <v>3112</v>
+        <v>3130</v>
       </c>
       <c r="G267" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B267,Station_Visual_Nodes!$J$2:$J$2000)+Q267,0)</f>
@@ -68257,7 +68252,7 @@
       </c>
       <c r="H267" s="23">
         <f t="shared" si="8"/>
-        <v>60.78125</v>
+        <v>61.1328125</v>
       </c>
       <c r="I267" s="23">
         <f t="shared" si="9"/>

--- a/data/master/yeoyuro_seoul_vector_map_coordinate_workbook.xlsx
+++ b/data/master/yeoyuro_seoul_vector_map_coordinate_workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\MyProject\yeoyuro_seoul_project\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38536995-ADE5-4424-96BE-58A69D2D2B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F94D2FD-51D5-45FF-9612-B6BAB8A1D45A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7125" yWindow="1545" windowWidth="28800" windowHeight="15345" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -3817,14 +3817,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -13411,14 +13404,14 @@
         <v>663</v>
       </c>
       <c r="I10" s="22">
-        <v>2864</v>
+        <v>2888</v>
       </c>
       <c r="J10" s="22">
         <v>980</v>
       </c>
       <c r="K10" s="23">
         <f t="shared" si="0"/>
-        <v>55.937499999999993</v>
+        <v>56.40625</v>
       </c>
       <c r="L10" s="23">
         <f t="shared" si="1"/>
@@ -13465,14 +13458,14 @@
         <v>663</v>
       </c>
       <c r="I11" s="22">
-        <v>3020</v>
+        <v>3064</v>
       </c>
       <c r="J11" s="22">
         <v>980</v>
       </c>
       <c r="K11" s="23">
         <f t="shared" si="0"/>
-        <v>58.984375</v>
+        <v>59.843749999999993</v>
       </c>
       <c r="L11" s="23">
         <f t="shared" si="1"/>
@@ -13958,7 +13951,7 @@
         <v>2816</v>
       </c>
       <c r="J20" s="22">
-        <v>1194</v>
+        <v>1208</v>
       </c>
       <c r="K20" s="23">
         <f t="shared" si="0"/>
@@ -13966,7 +13959,7 @@
       </c>
       <c r="L20" s="23">
         <f t="shared" si="1"/>
-        <v>41.458333333333336</v>
+        <v>41.944444444444443</v>
       </c>
       <c r="M20" s="2">
         <v>10</v>
@@ -14012,7 +14005,7 @@
         <v>2896</v>
       </c>
       <c r="J21" s="22">
-        <v>1244</v>
+        <v>1272</v>
       </c>
       <c r="K21" s="23">
         <f t="shared" si="0"/>
@@ -14020,7 +14013,7 @@
       </c>
       <c r="L21" s="23">
         <f t="shared" si="1"/>
-        <v>43.194444444444443</v>
+        <v>44.166666666666664</v>
       </c>
       <c r="M21" s="2">
         <v>10</v>
@@ -14066,7 +14059,7 @@
         <v>2972</v>
       </c>
       <c r="J22" s="22">
-        <v>1294</v>
+        <v>1336</v>
       </c>
       <c r="K22" s="23">
         <f t="shared" si="0"/>
@@ -14074,7 +14067,7 @@
       </c>
       <c r="L22" s="23">
         <f t="shared" si="1"/>
-        <v>44.930555555555557</v>
+        <v>46.388888888888893</v>
       </c>
       <c r="M22" s="2">
         <v>10</v>
@@ -24511,14 +24504,14 @@
         <v>663</v>
       </c>
       <c r="I215" s="22">
-        <v>3664</v>
+        <v>3604</v>
       </c>
       <c r="J215" s="22">
         <v>636</v>
       </c>
       <c r="K215" s="23">
         <f t="shared" si="6"/>
-        <v>71.5625</v>
+        <v>70.390625</v>
       </c>
       <c r="L215" s="23">
         <f t="shared" si="7"/>
@@ -24565,18 +24558,18 @@
         <v>663</v>
       </c>
       <c r="I216" s="22">
-        <v>3664</v>
+        <v>3744</v>
       </c>
       <c r="J216" s="22">
-        <v>792</v>
+        <v>636</v>
       </c>
       <c r="K216" s="23">
         <f t="shared" si="6"/>
-        <v>71.5625</v>
+        <v>73.125</v>
       </c>
       <c r="L216" s="23">
         <f t="shared" si="7"/>
-        <v>27.500000000000004</v>
+        <v>22.083333333333332</v>
       </c>
       <c r="M216" s="2">
         <v>10</v>
@@ -24619,18 +24612,18 @@
         <v>663</v>
       </c>
       <c r="I217" s="22">
-        <v>3664</v>
+        <v>3744</v>
       </c>
       <c r="J217" s="22">
-        <v>948</v>
+        <v>860</v>
       </c>
       <c r="K217" s="23">
         <f t="shared" si="6"/>
-        <v>71.5625</v>
+        <v>73.125</v>
       </c>
       <c r="L217" s="23">
         <f t="shared" si="7"/>
-        <v>32.916666666666664</v>
+        <v>29.861111111111111</v>
       </c>
       <c r="M217" s="2">
         <v>10</v>
@@ -24676,7 +24669,7 @@
         <v>3064</v>
       </c>
       <c r="J218" s="22">
-        <v>408</v>
+        <v>458</v>
       </c>
       <c r="K218" s="23">
         <f t="shared" si="6"/>
@@ -24684,7 +24677,7 @@
       </c>
       <c r="L218" s="23">
         <f t="shared" si="7"/>
-        <v>14.166666666666666</v>
+        <v>15.902777777777777</v>
       </c>
       <c r="M218" s="2">
         <v>10</v>
@@ -24730,7 +24723,7 @@
         <v>3064</v>
       </c>
       <c r="J219" s="22">
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="K219" s="23">
         <f t="shared" si="6"/>
@@ -24738,7 +24731,7 @@
       </c>
       <c r="L219" s="23">
         <f t="shared" si="7"/>
-        <v>11.25</v>
+        <v>12.361111111111111</v>
       </c>
       <c r="M219" s="2">
         <v>10</v>
@@ -30041,7 +30034,7 @@
   <autoFilter ref="A1:R316" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A2:R316">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>COUNTIFS($I$2:$I$316,$I2,$J$2:$J$316,$J2,$D$2:$D$316,"&lt;&gt;"&amp;$D2)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -40839,7 +40832,7 @@
       </c>
       <c r="F10" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B10,Station_Visual_Nodes!$I$2:$I$2000)+N10,0)</f>
-        <v>2864</v>
+        <v>2888</v>
       </c>
       <c r="G10" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B10,Station_Visual_Nodes!$J$2:$J$2000)+O10,0)</f>
@@ -40847,7 +40840,7 @@
       </c>
       <c r="H10" s="23">
         <f t="shared" si="0"/>
-        <v>55.937499999999993</v>
+        <v>56.40625</v>
       </c>
       <c r="I10" s="23">
         <f t="shared" si="1"/>
@@ -40888,7 +40881,7 @@
       </c>
       <c r="F11" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B11,Station_Visual_Nodes!$I$2:$I$2000)+N11,0)</f>
-        <v>3020</v>
+        <v>3064</v>
       </c>
       <c r="G11" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B11,Station_Visual_Nodes!$J$2:$J$2000)+O11,0)</f>
@@ -40896,7 +40889,7 @@
       </c>
       <c r="H11" s="23">
         <f t="shared" si="0"/>
-        <v>58.984375</v>
+        <v>59.843749999999993</v>
       </c>
       <c r="I11" s="23">
         <f t="shared" si="1"/>
@@ -41378,7 +41371,7 @@
       </c>
       <c r="G21" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B21,Station_Visual_Nodes!$J$2:$J$2000)+O21,0)</f>
-        <v>1294</v>
+        <v>1336</v>
       </c>
       <c r="H21" s="23">
         <f t="shared" si="0"/>
@@ -41386,7 +41379,7 @@
       </c>
       <c r="I21" s="23">
         <f t="shared" si="1"/>
-        <v>44.930555555555557</v>
+        <v>46.388888888888893</v>
       </c>
       <c r="J21" s="2">
         <v>24</v>
@@ -49551,7 +49544,7 @@
       </c>
       <c r="F188" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B188,Station_Visual_Nodes!$I$2:$I$2000)+N188,0)</f>
-        <v>3664</v>
+        <v>3604</v>
       </c>
       <c r="G188" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B188,Station_Visual_Nodes!$J$2:$J$2000)+O188,0)</f>
@@ -49559,7 +49552,7 @@
       </c>
       <c r="H188" s="23">
         <f t="shared" si="4"/>
-        <v>71.5625</v>
+        <v>70.390625</v>
       </c>
       <c r="I188" s="23">
         <f t="shared" si="5"/>
@@ -49600,19 +49593,19 @@
       </c>
       <c r="F189" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B189,Station_Visual_Nodes!$I$2:$I$2000)+N189,0)</f>
-        <v>3664</v>
+        <v>3744</v>
       </c>
       <c r="G189" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B189,Station_Visual_Nodes!$J$2:$J$2000)+O189,0)</f>
-        <v>792</v>
+        <v>636</v>
       </c>
       <c r="H189" s="23">
         <f t="shared" si="4"/>
-        <v>71.5625</v>
+        <v>73.125</v>
       </c>
       <c r="I189" s="23">
         <f t="shared" si="5"/>
-        <v>27.500000000000004</v>
+        <v>22.083333333333332</v>
       </c>
       <c r="J189" s="2">
         <v>24</v>
@@ -49649,19 +49642,19 @@
       </c>
       <c r="F190" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B190,Station_Visual_Nodes!$I$2:$I$2000)+N190,0)</f>
-        <v>3664</v>
+        <v>3744</v>
       </c>
       <c r="G190" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B190,Station_Visual_Nodes!$J$2:$J$2000)+O190,0)</f>
-        <v>948</v>
+        <v>860</v>
       </c>
       <c r="H190" s="23">
         <f t="shared" si="4"/>
-        <v>71.5625</v>
+        <v>73.125</v>
       </c>
       <c r="I190" s="23">
         <f t="shared" si="5"/>
-        <v>32.916666666666664</v>
+        <v>29.861111111111111</v>
       </c>
       <c r="J190" s="2">
         <v>24</v>
@@ -49702,7 +49695,7 @@
       </c>
       <c r="G191" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B191,Station_Visual_Nodes!$J$2:$J$2000)+O191,0)</f>
-        <v>408</v>
+        <v>458</v>
       </c>
       <c r="H191" s="23">
         <f t="shared" si="4"/>
@@ -49710,7 +49703,7 @@
       </c>
       <c r="I191" s="23">
         <f t="shared" si="5"/>
-        <v>14.166666666666666</v>
+        <v>15.902777777777777</v>
       </c>
       <c r="J191" s="2">
         <v>24</v>
@@ -49751,7 +49744,7 @@
       </c>
       <c r="G192" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B192,Station_Visual_Nodes!$J$2:$J$2000)+O192,0)</f>
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="H192" s="23">
         <f t="shared" si="4"/>
@@ -49759,7 +49752,7 @@
       </c>
       <c r="I192" s="23">
         <f t="shared" si="5"/>
-        <v>11.25</v>
+        <v>12.361111111111111</v>
       </c>
       <c r="J192" s="2">
         <v>24</v>
@@ -54122,7 +54115,7 @@
       </c>
       <c r="F10" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B10,Station_Visual_Nodes!$I$2:$I$2000)+P10,0)</f>
-        <v>2864</v>
+        <v>2888</v>
       </c>
       <c r="G10" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B10,Station_Visual_Nodes!$J$2:$J$2000)+Q10,0)</f>
@@ -54130,7 +54123,7 @@
       </c>
       <c r="H10" s="23">
         <f t="shared" si="0"/>
-        <v>55.937499999999993</v>
+        <v>56.40625</v>
       </c>
       <c r="I10" s="23">
         <f t="shared" si="1"/>
@@ -54177,7 +54170,7 @@
       </c>
       <c r="F11" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B11,Station_Visual_Nodes!$I$2:$I$2000)+P11,0)</f>
-        <v>3020</v>
+        <v>3064</v>
       </c>
       <c r="G11" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B11,Station_Visual_Nodes!$J$2:$J$2000)+Q11,0)</f>
@@ -54185,7 +54178,7 @@
       </c>
       <c r="H11" s="23">
         <f t="shared" si="0"/>
-        <v>58.984375</v>
+        <v>59.843749999999993</v>
       </c>
       <c r="I11" s="23">
         <f t="shared" si="1"/>
@@ -54727,7 +54720,7 @@
       </c>
       <c r="G21" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B21,Station_Visual_Nodes!$J$2:$J$2000)+Q21,0)</f>
-        <v>1294</v>
+        <v>1336</v>
       </c>
       <c r="H21" s="23">
         <f t="shared" si="0"/>
@@ -54735,7 +54728,7 @@
       </c>
       <c r="I21" s="23">
         <f t="shared" si="1"/>
-        <v>44.930555555555557</v>
+        <v>46.388888888888893</v>
       </c>
       <c r="J21" s="2">
         <v>10.5</v>
@@ -63907,7 +63900,7 @@
       </c>
       <c r="F188" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B188,Station_Visual_Nodes!$I$2:$I$2000)+P188,0)</f>
-        <v>3664</v>
+        <v>3604</v>
       </c>
       <c r="G188" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B188,Station_Visual_Nodes!$J$2:$J$2000)+Q188,0)</f>
@@ -63915,7 +63908,7 @@
       </c>
       <c r="H188" s="23">
         <f t="shared" si="4"/>
-        <v>71.5625</v>
+        <v>70.390625</v>
       </c>
       <c r="I188" s="23">
         <f t="shared" si="5"/>
@@ -63962,19 +63955,19 @@
       </c>
       <c r="F189" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B189,Station_Visual_Nodes!$I$2:$I$2000)+P189,0)</f>
-        <v>3664</v>
+        <v>3744</v>
       </c>
       <c r="G189" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B189,Station_Visual_Nodes!$J$2:$J$2000)+Q189,0)</f>
-        <v>792</v>
+        <v>636</v>
       </c>
       <c r="H189" s="23">
         <f t="shared" si="4"/>
-        <v>71.5625</v>
+        <v>73.125</v>
       </c>
       <c r="I189" s="23">
         <f t="shared" si="5"/>
-        <v>27.500000000000004</v>
+        <v>22.083333333333332</v>
       </c>
       <c r="J189" s="2">
         <v>10.5</v>
@@ -64017,19 +64010,19 @@
       </c>
       <c r="F190" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B190,Station_Visual_Nodes!$I$2:$I$2000)+P190,0)</f>
-        <v>3664</v>
+        <v>3744</v>
       </c>
       <c r="G190" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B190,Station_Visual_Nodes!$J$2:$J$2000)+Q190,0)</f>
-        <v>948</v>
+        <v>860</v>
       </c>
       <c r="H190" s="23">
         <f t="shared" si="4"/>
-        <v>71.5625</v>
+        <v>73.125</v>
       </c>
       <c r="I190" s="23">
         <f t="shared" si="5"/>
-        <v>32.916666666666664</v>
+        <v>29.861111111111111</v>
       </c>
       <c r="J190" s="2">
         <v>10.5</v>
@@ -64076,7 +64069,7 @@
       </c>
       <c r="G191" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B191,Station_Visual_Nodes!$J$2:$J$2000)+Q191,0)</f>
-        <v>408</v>
+        <v>458</v>
       </c>
       <c r="H191" s="23">
         <f t="shared" si="4"/>
@@ -64084,7 +64077,7 @@
       </c>
       <c r="I191" s="23">
         <f t="shared" si="5"/>
-        <v>14.166666666666666</v>
+        <v>15.902777777777777</v>
       </c>
       <c r="J191" s="2">
         <v>10.5</v>
@@ -64131,7 +64124,7 @@
       </c>
       <c r="G192" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B192,Station_Visual_Nodes!$J$2:$J$2000)+Q192,0)</f>
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="H192" s="23">
         <f t="shared" si="4"/>
@@ -64139,7 +64132,7 @@
       </c>
       <c r="I192" s="23">
         <f t="shared" si="5"/>
-        <v>11.25</v>
+        <v>12.361111111111111</v>
       </c>
       <c r="J192" s="2">
         <v>10.5</v>

--- a/data/master/yeoyuro_seoul_vector_map_coordinate_workbook.xlsx
+++ b/data/master/yeoyuro_seoul_vector_map_coordinate_workbook.xlsx
@@ -65121,7 +65121,7 @@
       </c>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="25" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="25" t="n">
         <v>0</v>
@@ -65263,10 +65263,10 @@
       </c>
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="25" t="n">
-        <v>-112</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="25" t="n">
-        <v>-130</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -65333,10 +65333,10 @@
       </c>
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="25" t="n">
-        <v>-31</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="25" t="n">
-        <v>-97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -65407,7 +65407,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="25" t="n">
-        <v>-126</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -65475,10 +65475,10 @@
       </c>
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="25" t="n">
-        <v>-94</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="25" t="n">
-        <v>-68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -65757,12 +65757,16 @@
           <t>default_from_click_area</t>
         </is>
       </c>
-      <c r="O12" s="2" t="n"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>역명 가로 -5 (5px 겹침 방지, D-068)</t>
+        </is>
+      </c>
       <c r="P12" s="25" t="n">
-        <v>43</v>
+        <v>-5</v>
       </c>
       <c r="Q12" s="25" t="n">
-        <v>-97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -65830,7 +65834,7 @@
       </c>
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="25" t="n">
-        <v>-45</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="25" t="n">
         <v>0</v>
@@ -65899,9 +65903,13 @@
           <t>default_from_click_area</t>
         </is>
       </c>
-      <c r="O14" s="2" t="n"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>역명 가로 -10 (5px 겹침 방지, D-068)</t>
+        </is>
+      </c>
       <c r="P14" s="25" t="n">
-        <v>45</v>
+        <v>-10</v>
       </c>
       <c r="Q14" s="25" t="n">
         <v>0</v>
@@ -65970,12 +65978,16 @@
           <t>default_from_click_area</t>
         </is>
       </c>
-      <c r="O15" s="2" t="n"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>역명 가로 +13 (5px 겹침 방지, D-068)</t>
+        </is>
+      </c>
       <c r="P15" s="25" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q15" s="25" t="n">
-        <v>-130</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -66043,10 +66055,10 @@
       </c>
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="25" t="n">
-        <v>-74</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="25" t="n">
-        <v>-68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -66117,7 +66129,7 @@
         <v>0</v>
       </c>
       <c r="Q17" s="25" t="n">
-        <v>-97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -66185,7 +66197,7 @@
       </c>
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="25" t="n">
-        <v>-53</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="25" t="n">
         <v>0</v>
@@ -66323,7 +66335,7 @@
       </c>
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="25" t="n">
-        <v>-31</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="25" t="n">
         <v>0</v>
@@ -66536,7 +66548,7 @@
       </c>
       <c r="O23" s="2" t="n"/>
       <c r="P23" s="25" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="25" t="n">
         <v>0</v>
@@ -66607,7 +66619,7 @@
       </c>
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="25" t="n">
-        <v>-31</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="25" t="n">
         <v>0</v>
@@ -66678,10 +66690,10 @@
       </c>
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="25" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="25" t="n">
-        <v>-53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -66749,10 +66761,10 @@
       </c>
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="25" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="25" t="n">
-        <v>-68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -66820,10 +66832,10 @@
       </c>
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="25" t="n">
-        <v>-93</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="25" t="n">
-        <v>-97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -66889,12 +66901,16 @@
           <t>default_from_click_area</t>
         </is>
       </c>
-      <c r="O28" s="2" t="n"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>역명 가로 +2 (5px 겹침 방지, D-068)</t>
+        </is>
+      </c>
       <c r="P28" s="25" t="n">
-        <v>-121</v>
+        <v>2</v>
       </c>
       <c r="Q28" s="25" t="n">
-        <v>-108</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -67604,7 +67620,7 @@
         <v>0</v>
       </c>
       <c r="Q38" s="25" t="n">
-        <v>-97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -67885,7 +67901,7 @@
       </c>
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="25" t="n">
-        <v>-109</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="25" t="n">
         <v>0</v>
@@ -67959,7 +67975,7 @@
         <v>0</v>
       </c>
       <c r="Q43" s="25" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -68098,7 +68114,7 @@
       </c>
       <c r="O45" s="2" t="n"/>
       <c r="P45" s="25" t="n">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="25" t="n">
         <v>0</v>
@@ -68666,10 +68682,10 @@
       </c>
       <c r="O53" s="2" t="n"/>
       <c r="P53" s="25" t="n">
-        <v>-94</v>
+        <v>0</v>
       </c>
       <c r="Q53" s="25" t="n">
-        <v>-126</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -70015,7 +70031,7 @@
       </c>
       <c r="O72" s="2" t="n"/>
       <c r="P72" s="25" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="Q72" s="25" t="n">
         <v>0</v>
@@ -70086,10 +70102,10 @@
       </c>
       <c r="O73" s="2" t="n"/>
       <c r="P73" s="25" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="Q73" s="25" t="n">
-        <v>-68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -70515,7 +70531,7 @@
         <v>0</v>
       </c>
       <c r="Q79" s="25" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -70938,10 +70954,10 @@
       </c>
       <c r="O85" s="2" t="n"/>
       <c r="P85" s="25" t="n">
-        <v>-76</v>
+        <v>0</v>
       </c>
       <c r="Q85" s="25" t="n">
-        <v>-97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -72216,10 +72232,10 @@
       </c>
       <c r="O103" s="2" t="n"/>
       <c r="P103" s="25" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="Q103" s="25" t="n">
-        <v>-53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -72500,7 +72516,7 @@
       </c>
       <c r="O107" s="2" t="n"/>
       <c r="P107" s="25" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="Q107" s="25" t="n">
         <v>0</v>
@@ -73067,7 +73083,7 @@
       </c>
       <c r="O115" s="2" t="n"/>
       <c r="P115" s="25" t="n">
-        <v>-62</v>
+        <v>0</v>
       </c>
       <c r="Q115" s="25" t="n">
         <v>0</v>
@@ -73777,7 +73793,7 @@
       </c>
       <c r="O125" s="2" t="n"/>
       <c r="P125" s="25" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="Q125" s="25" t="n">
         <v>0</v>
@@ -73922,7 +73938,7 @@
         <v>0</v>
       </c>
       <c r="Q127" s="25" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -74132,7 +74148,7 @@
       </c>
       <c r="O130" s="2" t="n"/>
       <c r="P130" s="25" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="Q130" s="25" t="n">
         <v>0</v>
@@ -77114,7 +77130,7 @@
       </c>
       <c r="O172" s="2" t="n"/>
       <c r="P172" s="25" t="n">
-        <v>-26</v>
+        <v>0</v>
       </c>
       <c r="Q172" s="25" t="n">
         <v>0</v>
@@ -77256,10 +77272,10 @@
       </c>
       <c r="O174" s="2" t="n"/>
       <c r="P174" s="25" t="n">
-        <v>-110</v>
+        <v>0</v>
       </c>
       <c r="Q174" s="25" t="n">
-        <v>-97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -77327,10 +77343,10 @@
       </c>
       <c r="O175" s="2" t="n"/>
       <c r="P175" s="25" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q175" s="25" t="n">
-        <v>-97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -77469,7 +77485,7 @@
       </c>
       <c r="O177" s="2" t="n"/>
       <c r="P177" s="25" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q177" s="25" t="n">
         <v>0</v>
@@ -77540,10 +77556,10 @@
       </c>
       <c r="O178" s="2" t="n"/>
       <c r="P178" s="25" t="n">
-        <v>-93</v>
+        <v>0</v>
       </c>
       <c r="Q178" s="25" t="n">
-        <v>-97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -79457,10 +79473,10 @@
       </c>
       <c r="O205" s="2" t="n"/>
       <c r="P205" s="25" t="n">
-        <v>-52</v>
+        <v>0</v>
       </c>
       <c r="Q205" s="25" t="n">
-        <v>-97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -79812,10 +79828,10 @@
       </c>
       <c r="O210" s="2" t="n"/>
       <c r="P210" s="25" t="n">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="Q210" s="25" t="n">
-        <v>-97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -80099,7 +80115,7 @@
         <v>0</v>
       </c>
       <c r="Q214" s="25" t="n">
-        <v>-97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -80238,7 +80254,7 @@
       </c>
       <c r="O216" s="2" t="n"/>
       <c r="P216" s="25" t="n">
-        <v>-35</v>
+        <v>0</v>
       </c>
       <c r="Q216" s="25" t="n">
         <v>0</v>
@@ -80309,10 +80325,10 @@
       </c>
       <c r="O217" s="2" t="n"/>
       <c r="P217" s="25" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="Q217" s="25" t="n">
-        <v>-97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -80520,9 +80536,13 @@
           <t>default_from_click_area</t>
         </is>
       </c>
-      <c r="O220" s="2" t="n"/>
+      <c r="O220" s="2" t="inlineStr">
+        <is>
+          <t>역명 가로 +7 (5px 겹침 방지, D-068)</t>
+        </is>
+      </c>
       <c r="P220" s="25" t="n">
-        <v>-26</v>
+        <v>7</v>
       </c>
       <c r="Q220" s="25" t="n">
         <v>0</v>
@@ -80593,10 +80613,10 @@
       </c>
       <c r="O221" s="2" t="n"/>
       <c r="P221" s="25" t="n">
-        <v>-61</v>
+        <v>0</v>
       </c>
       <c r="Q221" s="25" t="n">
-        <v>-97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -80735,10 +80755,10 @@
       </c>
       <c r="O223" s="2" t="n"/>
       <c r="P223" s="25" t="n">
-        <v>-110</v>
+        <v>0</v>
       </c>
       <c r="Q223" s="25" t="n">
-        <v>-97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -80948,7 +80968,7 @@
       </c>
       <c r="O226" s="2" t="n"/>
       <c r="P226" s="25" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="Q226" s="25" t="n">
         <v>0</v>
@@ -81090,10 +81110,10 @@
       </c>
       <c r="O228" s="2" t="n"/>
       <c r="P228" s="25" t="n">
-        <v>-35</v>
+        <v>0</v>
       </c>
       <c r="Q228" s="25" t="n">
-        <v>-97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -81161,7 +81181,7 @@
       </c>
       <c r="O229" s="2" t="n"/>
       <c r="P229" s="25" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="Q229" s="25" t="n">
         <v>0</v>
@@ -82153,10 +82173,10 @@
       </c>
       <c r="O243" s="2" t="n"/>
       <c r="P243" s="25" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="Q243" s="25" t="n">
-        <v>-97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -83356,7 +83376,7 @@
       </c>
       <c r="O260" s="2" t="n"/>
       <c r="P260" s="25" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="Q260" s="25" t="n">
         <v>0</v>
@@ -83427,10 +83447,10 @@
       </c>
       <c r="O261" s="2" t="n"/>
       <c r="P261" s="25" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q261" s="25" t="n">
-        <v>-97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -83569,7 +83589,7 @@
       </c>
       <c r="O263" s="2" t="n"/>
       <c r="P263" s="25" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q263" s="25" t="n">
         <v>0</v>
@@ -83639,10 +83659,10 @@
       </c>
       <c r="O264" s="2" t="n"/>
       <c r="P264" s="25" t="n">
-        <v>-93</v>
+        <v>0</v>
       </c>
       <c r="Q264" s="25" t="n">
-        <v>-53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -83709,7 +83729,7 @@
       </c>
       <c r="O265" s="2" t="n"/>
       <c r="P265" s="25" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="Q265" s="25" t="n">
         <v>0</v>

--- a/data/master/yeoyuro_seoul_vector_map_coordinate_workbook.xlsx
+++ b/data/master/yeoyuro_seoul_vector_map_coordinate_workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\MyProject\yeoyuro_seoul_project\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75740A25-D9B4-4E70-869B-8688D5BC1864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2442B514-51A4-4E50-BD92-3396B9F7712C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7125" yWindow="1545" windowWidth="28800" windowHeight="15345" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24681,18 +24681,18 @@
         <v>21</v>
       </c>
       <c r="I218" s="22">
-        <v>3194</v>
+        <v>3064</v>
       </c>
       <c r="J218" s="22">
-        <v>458</v>
+        <v>240</v>
       </c>
       <c r="K218" s="23">
         <f t="shared" si="6"/>
-        <v>62.382812499999993</v>
+        <v>59.843749999999993</v>
       </c>
       <c r="L218" s="23">
         <f t="shared" si="7"/>
-        <v>15.902777777777777</v>
+        <v>8.3333333333333321</v>
       </c>
       <c r="M218" s="2">
         <v>10</v>
@@ -24738,7 +24738,7 @@
         <v>3194</v>
       </c>
       <c r="J219" s="22">
-        <v>356</v>
+        <v>240</v>
       </c>
       <c r="K219" s="23">
         <f t="shared" si="6"/>
@@ -24746,7 +24746,7 @@
       </c>
       <c r="L219" s="23">
         <f t="shared" si="7"/>
-        <v>12.361111111111111</v>
+        <v>8.3333333333333321</v>
       </c>
       <c r="M219" s="2">
         <v>10</v>
@@ -24789,14 +24789,14 @@
         <v>21</v>
       </c>
       <c r="I220" s="22">
-        <v>3194</v>
+        <v>3324</v>
       </c>
       <c r="J220" s="22">
         <v>240</v>
       </c>
       <c r="K220" s="23">
         <f t="shared" si="6"/>
-        <v>62.382812499999993</v>
+        <v>64.921875</v>
       </c>
       <c r="L220" s="23">
         <f t="shared" si="7"/>
@@ -49706,19 +49706,19 @@
       </c>
       <c r="F191" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B191,Station_Visual_Nodes!$I$2:$I$2000)+N191,0)</f>
-        <v>3194</v>
+        <v>3064</v>
       </c>
       <c r="G191" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B191,Station_Visual_Nodes!$J$2:$J$2000)+O191,0)</f>
-        <v>458</v>
+        <v>240</v>
       </c>
       <c r="H191" s="23">
         <f t="shared" si="4"/>
-        <v>62.382812499999993</v>
+        <v>59.843749999999993</v>
       </c>
       <c r="I191" s="23">
         <f t="shared" si="5"/>
-        <v>15.902777777777777</v>
+        <v>8.3333333333333321</v>
       </c>
       <c r="J191" s="2">
         <v>24</v>
@@ -49759,7 +49759,7 @@
       </c>
       <c r="G192" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B192,Station_Visual_Nodes!$J$2:$J$2000)+O192,0)</f>
-        <v>356</v>
+        <v>240</v>
       </c>
       <c r="H192" s="23">
         <f t="shared" si="4"/>
@@ -49767,7 +49767,7 @@
       </c>
       <c r="I192" s="23">
         <f t="shared" si="5"/>
-        <v>12.361111111111111</v>
+        <v>8.3333333333333321</v>
       </c>
       <c r="J192" s="2">
         <v>24</v>
@@ -49804,7 +49804,7 @@
       </c>
       <c r="F193" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B193,Station_Visual_Nodes!$I$2:$I$2000)+N193,0)</f>
-        <v>3194</v>
+        <v>3324</v>
       </c>
       <c r="G193" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B193,Station_Visual_Nodes!$J$2:$J$2000)+O193,0)</f>
@@ -49812,7 +49812,7 @@
       </c>
       <c r="H193" s="23">
         <f t="shared" si="4"/>
-        <v>62.382812499999993</v>
+        <v>64.921875</v>
       </c>
       <c r="I193" s="23">
         <f t="shared" si="5"/>
@@ -64088,19 +64088,19 @@
       </c>
       <c r="F191" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B191,Station_Visual_Nodes!$I$2:$I$2000)+P191,0)</f>
-        <v>3194</v>
+        <v>3064</v>
       </c>
       <c r="G191" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B191,Station_Visual_Nodes!$J$2:$J$2000)+Q191,0)</f>
-        <v>458</v>
+        <v>240</v>
       </c>
       <c r="H191" s="23">
         <f t="shared" si="4"/>
-        <v>62.382812499999993</v>
+        <v>59.843749999999993</v>
       </c>
       <c r="I191" s="23">
         <f t="shared" si="5"/>
-        <v>15.902777777777777</v>
+        <v>8.3333333333333321</v>
       </c>
       <c r="J191" s="2">
         <v>10.5</v>
@@ -64147,7 +64147,7 @@
       </c>
       <c r="G192" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B192,Station_Visual_Nodes!$J$2:$J$2000)+Q192,0)</f>
-        <v>356</v>
+        <v>240</v>
       </c>
       <c r="H192" s="23">
         <f t="shared" si="4"/>
@@ -64155,7 +64155,7 @@
       </c>
       <c r="I192" s="23">
         <f t="shared" si="5"/>
-        <v>12.361111111111111</v>
+        <v>8.3333333333333321</v>
       </c>
       <c r="J192" s="2">
         <v>10.5</v>
@@ -64198,7 +64198,7 @@
       </c>
       <c r="F193" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B193,Station_Visual_Nodes!$I$2:$I$2000)+P193,0)</f>
-        <v>3194</v>
+        <v>3324</v>
       </c>
       <c r="G193" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B193,Station_Visual_Nodes!$J$2:$J$2000)+Q193,0)</f>
@@ -64206,7 +64206,7 @@
       </c>
       <c r="H193" s="23">
         <f t="shared" si="4"/>
-        <v>62.382812499999993</v>
+        <v>64.921875</v>
       </c>
       <c r="I193" s="23">
         <f t="shared" si="5"/>

--- a/data/master/yeoyuro_seoul_vector_map_coordinate_workbook.xlsx
+++ b/data/master/yeoyuro_seoul_vector_map_coordinate_workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\MyProject\yeoyuro_seoul_project\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2442B514-51A4-4E50-BD92-3396B9F7712C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8327742E-E5FD-42FC-A21A-3FD3B81E2F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7125" yWindow="1545" windowWidth="28800" windowHeight="15345" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13473,14 +13473,14 @@
         <v>21</v>
       </c>
       <c r="I11" s="22">
-        <v>3064</v>
+        <v>3080</v>
       </c>
       <c r="J11" s="22">
         <v>980</v>
       </c>
       <c r="K11" s="23">
         <f t="shared" si="0"/>
-        <v>59.843749999999993</v>
+        <v>60.15625</v>
       </c>
       <c r="L11" s="23">
         <f t="shared" si="1"/>
@@ -17102,7 +17102,7 @@
         <v>2480</v>
       </c>
       <c r="J78" s="22">
-        <v>1556</v>
+        <v>1564</v>
       </c>
       <c r="K78" s="23">
         <f t="shared" si="2"/>
@@ -17110,7 +17110,7 @@
       </c>
       <c r="L78" s="23">
         <f t="shared" si="3"/>
-        <v>54.027777777777771</v>
+        <v>54.30555555555555</v>
       </c>
       <c r="M78" s="2">
         <v>10</v>
@@ -17156,7 +17156,7 @@
         <v>2480</v>
       </c>
       <c r="J79" s="22">
-        <v>1636</v>
+        <v>1652</v>
       </c>
       <c r="K79" s="23">
         <f t="shared" si="2"/>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="L79" s="23">
         <f t="shared" si="3"/>
-        <v>56.805555555555557</v>
+        <v>57.361111111111107</v>
       </c>
       <c r="M79" s="2">
         <v>10</v>
@@ -17210,7 +17210,7 @@
         <v>2480</v>
       </c>
       <c r="J80" s="22">
-        <v>1760</v>
+        <v>1750</v>
       </c>
       <c r="K80" s="23">
         <f t="shared" si="2"/>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="L80" s="23">
         <f t="shared" si="3"/>
-        <v>61.111111111111114</v>
+        <v>60.763888888888886</v>
       </c>
       <c r="M80" s="2">
         <v>10</v>
@@ -17264,7 +17264,7 @@
         <v>2480</v>
       </c>
       <c r="J81" s="22">
-        <v>1828</v>
+        <v>1820</v>
       </c>
       <c r="K81" s="23">
         <f t="shared" si="2"/>
@@ -17272,7 +17272,7 @@
       </c>
       <c r="L81" s="23">
         <f t="shared" si="3"/>
-        <v>63.472222222222221</v>
+        <v>63.194444444444443</v>
       </c>
       <c r="M81" s="2">
         <v>10</v>
@@ -17318,7 +17318,7 @@
         <v>2480</v>
       </c>
       <c r="J82" s="22">
-        <v>1884</v>
+        <v>1892</v>
       </c>
       <c r="K82" s="23">
         <f t="shared" si="2"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="L82" s="23">
         <f t="shared" si="3"/>
-        <v>65.416666666666671</v>
+        <v>65.694444444444443</v>
       </c>
       <c r="M82" s="2">
         <v>10</v>
@@ -18397,14 +18397,14 @@
         <v>21</v>
       </c>
       <c r="I102" s="22">
-        <v>3064</v>
+        <v>3080</v>
       </c>
       <c r="J102" s="22">
         <v>648</v>
       </c>
       <c r="K102" s="23">
         <f t="shared" si="2"/>
-        <v>59.843749999999993</v>
+        <v>60.15625</v>
       </c>
       <c r="L102" s="23">
         <f t="shared" si="3"/>
@@ -18451,14 +18451,14 @@
         <v>21</v>
       </c>
       <c r="I103" s="22">
-        <v>2908</v>
+        <v>2920</v>
       </c>
       <c r="J103" s="22">
         <v>648</v>
       </c>
       <c r="K103" s="23">
         <f t="shared" si="2"/>
-        <v>56.796875</v>
+        <v>57.03125</v>
       </c>
       <c r="L103" s="23">
         <f t="shared" si="3"/>
@@ -18505,14 +18505,14 @@
         <v>21</v>
       </c>
       <c r="I104" s="22">
-        <v>2752</v>
+        <v>2760</v>
       </c>
       <c r="J104" s="22">
         <v>648</v>
       </c>
       <c r="K104" s="23">
         <f t="shared" si="2"/>
-        <v>53.75</v>
+        <v>53.90625</v>
       </c>
       <c r="L104" s="23">
         <f t="shared" si="3"/>
@@ -18559,14 +18559,14 @@
         <v>21</v>
       </c>
       <c r="I105" s="22">
-        <v>2596</v>
+        <v>2600</v>
       </c>
       <c r="J105" s="22">
         <v>648</v>
       </c>
       <c r="K105" s="23">
         <f t="shared" si="2"/>
-        <v>50.703125000000007</v>
+        <v>50.78125</v>
       </c>
       <c r="L105" s="23">
         <f t="shared" si="3"/>
@@ -21271,14 +21271,14 @@
         <v>377</v>
       </c>
       <c r="I155" s="22">
-        <v>3084</v>
+        <v>3080</v>
       </c>
       <c r="J155" s="22">
         <v>1144</v>
       </c>
       <c r="K155" s="23">
         <f t="shared" si="4"/>
-        <v>60.234374999999993</v>
+        <v>60.15625</v>
       </c>
       <c r="L155" s="23">
         <f t="shared" si="5"/>
@@ -22734,7 +22734,7 @@
         <v>1378</v>
       </c>
       <c r="J182" s="22">
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="K182" s="23">
         <f t="shared" si="4"/>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="L182" s="23">
         <f t="shared" si="5"/>
-        <v>11.25</v>
+        <v>12.361111111111111</v>
       </c>
       <c r="M182" s="2">
         <v>10</v>
@@ -24137,14 +24137,14 @@
         <v>21</v>
       </c>
       <c r="I208" s="22">
-        <v>2660</v>
+        <v>2666</v>
       </c>
       <c r="J208" s="22">
         <v>768</v>
       </c>
       <c r="K208" s="23">
         <f t="shared" si="6"/>
-        <v>51.953125</v>
+        <v>52.070312500000007</v>
       </c>
       <c r="L208" s="23">
         <f t="shared" si="7"/>
@@ -24193,14 +24193,14 @@
         <v>21</v>
       </c>
       <c r="I209" s="22">
-        <v>2792</v>
+        <v>2804</v>
       </c>
       <c r="J209" s="22">
         <v>768</v>
       </c>
       <c r="K209" s="23">
         <f t="shared" si="6"/>
-        <v>54.53125</v>
+        <v>54.765624999999993</v>
       </c>
       <c r="L209" s="23">
         <f t="shared" si="7"/>
@@ -24249,14 +24249,14 @@
         <v>21</v>
       </c>
       <c r="I210" s="22">
-        <v>2924</v>
+        <v>2942</v>
       </c>
       <c r="J210" s="22">
         <v>768</v>
       </c>
       <c r="K210" s="23">
         <f t="shared" si="6"/>
-        <v>57.109374999999993</v>
+        <v>57.4609375</v>
       </c>
       <c r="L210" s="23">
         <f t="shared" si="7"/>
@@ -24303,14 +24303,14 @@
         <v>21</v>
       </c>
       <c r="I211" s="22">
-        <v>3056</v>
+        <v>3080</v>
       </c>
       <c r="J211" s="22">
         <v>768</v>
       </c>
       <c r="K211" s="23">
         <f t="shared" si="6"/>
-        <v>59.687500000000007</v>
+        <v>60.15625</v>
       </c>
       <c r="L211" s="23">
         <f t="shared" si="7"/>
@@ -24357,14 +24357,14 @@
         <v>21</v>
       </c>
       <c r="I212" s="22">
-        <v>3188</v>
+        <v>3200</v>
       </c>
       <c r="J212" s="22">
         <v>768</v>
       </c>
       <c r="K212" s="23">
         <f t="shared" si="6"/>
-        <v>62.265625</v>
+        <v>62.5</v>
       </c>
       <c r="L212" s="23">
         <f t="shared" si="7"/>
@@ -25599,14 +25599,14 @@
         <v>21</v>
       </c>
       <c r="I235" s="22">
-        <v>3078</v>
+        <v>3080</v>
       </c>
       <c r="J235" s="22">
         <v>1364</v>
       </c>
       <c r="K235" s="23">
         <f t="shared" si="6"/>
-        <v>60.1171875</v>
+        <v>60.15625</v>
       </c>
       <c r="L235" s="23">
         <f t="shared" si="7"/>
@@ -40896,7 +40896,7 @@
       </c>
       <c r="F11" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B11,Station_Visual_Nodes!$I$2:$I$2000)+N11,0)</f>
-        <v>3064</v>
+        <v>3080</v>
       </c>
       <c r="G11" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B11,Station_Visual_Nodes!$J$2:$J$2000)+O11,0)</f>
@@ -40904,7 +40904,7 @@
       </c>
       <c r="H11" s="23">
         <f t="shared" si="0"/>
-        <v>59.843749999999993</v>
+        <v>60.15625</v>
       </c>
       <c r="I11" s="23">
         <f t="shared" si="1"/>
@@ -43983,7 +43983,7 @@
       </c>
       <c r="G74" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B74,Station_Visual_Nodes!$J$2:$J$2000)+O74,0)</f>
-        <v>1556</v>
+        <v>1564</v>
       </c>
       <c r="H74" s="23">
         <f t="shared" si="2"/>
@@ -43991,7 +43991,7 @@
       </c>
       <c r="I74" s="23">
         <f t="shared" si="3"/>
-        <v>54.027777777777771</v>
+        <v>54.30555555555555</v>
       </c>
       <c r="J74" s="2">
         <v>24</v>
@@ -44032,7 +44032,7 @@
       </c>
       <c r="G75" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B75,Station_Visual_Nodes!$J$2:$J$2000)+O75,0)</f>
-        <v>1636</v>
+        <v>1652</v>
       </c>
       <c r="H75" s="23">
         <f t="shared" si="2"/>
@@ -44040,7 +44040,7 @@
       </c>
       <c r="I75" s="23">
         <f t="shared" si="3"/>
-        <v>56.805555555555557</v>
+        <v>57.361111111111107</v>
       </c>
       <c r="J75" s="2">
         <v>24</v>
@@ -44081,7 +44081,7 @@
       </c>
       <c r="G76" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B76,Station_Visual_Nodes!$J$2:$J$2000)+O76,0)</f>
-        <v>1760</v>
+        <v>1750</v>
       </c>
       <c r="H76" s="23">
         <f t="shared" si="2"/>
@@ -44089,7 +44089,7 @@
       </c>
       <c r="I76" s="23">
         <f t="shared" si="3"/>
-        <v>61.111111111111114</v>
+        <v>60.763888888888886</v>
       </c>
       <c r="J76" s="2">
         <v>24</v>
@@ -44130,7 +44130,7 @@
       </c>
       <c r="G77" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B77,Station_Visual_Nodes!$J$2:$J$2000)+O77,0)</f>
-        <v>1828</v>
+        <v>1820</v>
       </c>
       <c r="H77" s="23">
         <f t="shared" si="2"/>
@@ -44138,7 +44138,7 @@
       </c>
       <c r="I77" s="23">
         <f t="shared" si="3"/>
-        <v>63.472222222222221</v>
+        <v>63.194444444444443</v>
       </c>
       <c r="J77" s="2">
         <v>24</v>
@@ -44179,7 +44179,7 @@
       </c>
       <c r="G78" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B78,Station_Visual_Nodes!$J$2:$J$2000)+O78,0)</f>
-        <v>1884</v>
+        <v>1892</v>
       </c>
       <c r="H78" s="23">
         <f t="shared" si="2"/>
@@ -44187,7 +44187,7 @@
       </c>
       <c r="I78" s="23">
         <f t="shared" si="3"/>
-        <v>65.416666666666671</v>
+        <v>65.694444444444443</v>
       </c>
       <c r="J78" s="2">
         <v>24</v>
@@ -45106,7 +45106,7 @@
       </c>
       <c r="F97" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B97,Station_Visual_Nodes!$I$2:$I$2000)+N97,0)</f>
-        <v>3064</v>
+        <v>3080</v>
       </c>
       <c r="G97" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B97,Station_Visual_Nodes!$J$2:$J$2000)+O97,0)</f>
@@ -45114,7 +45114,7 @@
       </c>
       <c r="H97" s="23">
         <f t="shared" si="2"/>
-        <v>59.843749999999993</v>
+        <v>60.15625</v>
       </c>
       <c r="I97" s="23">
         <f t="shared" si="3"/>
@@ -45155,7 +45155,7 @@
       </c>
       <c r="F98" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B98,Station_Visual_Nodes!$I$2:$I$2000)+N98,0)</f>
-        <v>2908</v>
+        <v>2920</v>
       </c>
       <c r="G98" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B98,Station_Visual_Nodes!$J$2:$J$2000)+O98,0)</f>
@@ -45163,7 +45163,7 @@
       </c>
       <c r="H98" s="23">
         <f t="shared" si="2"/>
-        <v>56.796875</v>
+        <v>57.03125</v>
       </c>
       <c r="I98" s="23">
         <f t="shared" si="3"/>
@@ -45204,7 +45204,7 @@
       </c>
       <c r="F99" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B99,Station_Visual_Nodes!$I$2:$I$2000)+N99,0)</f>
-        <v>2752</v>
+        <v>2760</v>
       </c>
       <c r="G99" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B99,Station_Visual_Nodes!$J$2:$J$2000)+O99,0)</f>
@@ -45212,7 +45212,7 @@
       </c>
       <c r="H99" s="23">
         <f t="shared" si="2"/>
-        <v>53.75</v>
+        <v>53.90625</v>
       </c>
       <c r="I99" s="23">
         <f t="shared" si="3"/>
@@ -45253,7 +45253,7 @@
       </c>
       <c r="F100" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B100,Station_Visual_Nodes!$I$2:$I$2000)+N100,0)</f>
-        <v>2596</v>
+        <v>2600</v>
       </c>
       <c r="G100" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B100,Station_Visual_Nodes!$J$2:$J$2000)+O100,0)</f>
@@ -45261,7 +45261,7 @@
       </c>
       <c r="H100" s="23">
         <f t="shared" si="2"/>
-        <v>50.703125000000007</v>
+        <v>50.78125</v>
       </c>
       <c r="I100" s="23">
         <f t="shared" si="3"/>
@@ -47109,7 +47109,7 @@
       </c>
       <c r="F138" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B138,Station_Visual_Nodes!$I$2:$I$2000)+N138,0)</f>
-        <v>3084</v>
+        <v>3080</v>
       </c>
       <c r="G138" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B138,Station_Visual_Nodes!$J$2:$J$2000)+O138,0)</f>
@@ -47117,7 +47117,7 @@
       </c>
       <c r="H138" s="23">
         <f t="shared" si="4"/>
-        <v>60.234374999999993</v>
+        <v>60.15625</v>
       </c>
       <c r="I138" s="23">
         <f t="shared" si="5"/>
@@ -48338,7 +48338,7 @@
       </c>
       <c r="G163" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B163,Station_Visual_Nodes!$J$2:$J$2000)+O163,0)</f>
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="H163" s="23">
         <f t="shared" si="4"/>
@@ -48346,7 +48346,7 @@
       </c>
       <c r="I163" s="23">
         <f t="shared" si="5"/>
-        <v>11.25</v>
+        <v>12.361111111111111</v>
       </c>
       <c r="J163" s="2">
         <v>24</v>
@@ -49216,7 +49216,7 @@
       </c>
       <c r="F181" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B181,Station_Visual_Nodes!$I$2:$I$2000)+N181,0)</f>
-        <v>2660</v>
+        <v>2666</v>
       </c>
       <c r="G181" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B181,Station_Visual_Nodes!$J$2:$J$2000)+O181,0)</f>
@@ -49224,7 +49224,7 @@
       </c>
       <c r="H181" s="23">
         <f t="shared" si="4"/>
-        <v>51.953125</v>
+        <v>52.070312500000007</v>
       </c>
       <c r="I181" s="23">
         <f t="shared" si="5"/>
@@ -49265,7 +49265,7 @@
       </c>
       <c r="F182" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B182,Station_Visual_Nodes!$I$2:$I$2000)+N182,0)</f>
-        <v>2792</v>
+        <v>2804</v>
       </c>
       <c r="G182" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B182,Station_Visual_Nodes!$J$2:$J$2000)+O182,0)</f>
@@ -49273,7 +49273,7 @@
       </c>
       <c r="H182" s="23">
         <f t="shared" si="4"/>
-        <v>54.53125</v>
+        <v>54.765624999999993</v>
       </c>
       <c r="I182" s="23">
         <f t="shared" si="5"/>
@@ -49314,7 +49314,7 @@
       </c>
       <c r="F183" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B183,Station_Visual_Nodes!$I$2:$I$2000)+N183,0)</f>
-        <v>2924</v>
+        <v>2942</v>
       </c>
       <c r="G183" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B183,Station_Visual_Nodes!$J$2:$J$2000)+O183,0)</f>
@@ -49322,7 +49322,7 @@
       </c>
       <c r="H183" s="23">
         <f t="shared" si="4"/>
-        <v>57.109374999999993</v>
+        <v>57.4609375</v>
       </c>
       <c r="I183" s="23">
         <f t="shared" si="5"/>
@@ -49363,7 +49363,7 @@
       </c>
       <c r="F184" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B184,Station_Visual_Nodes!$I$2:$I$2000)+N184,0)</f>
-        <v>3056</v>
+        <v>3080</v>
       </c>
       <c r="G184" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B184,Station_Visual_Nodes!$J$2:$J$2000)+O184,0)</f>
@@ -49371,7 +49371,7 @@
       </c>
       <c r="H184" s="23">
         <f t="shared" si="4"/>
-        <v>59.687500000000007</v>
+        <v>60.15625</v>
       </c>
       <c r="I184" s="23">
         <f t="shared" si="5"/>
@@ -49412,7 +49412,7 @@
       </c>
       <c r="F185" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B185,Station_Visual_Nodes!$I$2:$I$2000)+N185,0)</f>
-        <v>3188</v>
+        <v>3200</v>
       </c>
       <c r="G185" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B185,Station_Visual_Nodes!$J$2:$J$2000)+O185,0)</f>
@@ -49420,7 +49420,7 @@
       </c>
       <c r="H185" s="23">
         <f t="shared" si="4"/>
-        <v>62.265625</v>
+        <v>62.5</v>
       </c>
       <c r="I185" s="23">
         <f t="shared" si="5"/>
@@ -50392,7 +50392,7 @@
       </c>
       <c r="F205" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B205,Station_Visual_Nodes!$I$2:$I$2000)+N205,0)</f>
-        <v>3078</v>
+        <v>3080</v>
       </c>
       <c r="G205" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B205,Station_Visual_Nodes!$J$2:$J$2000)+O205,0)</f>
@@ -50400,7 +50400,7 @@
       </c>
       <c r="H205" s="23">
         <f t="shared" si="6"/>
-        <v>60.1171875</v>
+        <v>60.15625</v>
       </c>
       <c r="I205" s="23">
         <f t="shared" si="7"/>
@@ -54185,7 +54185,7 @@
       </c>
       <c r="F11" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B11,Station_Visual_Nodes!$I$2:$I$2000)+P11,0)</f>
-        <v>3064</v>
+        <v>3080</v>
       </c>
       <c r="G11" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B11,Station_Visual_Nodes!$J$2:$J$2000)+Q11,0)</f>
@@ -54193,7 +54193,7 @@
       </c>
       <c r="H11" s="23">
         <f t="shared" si="0"/>
-        <v>59.843749999999993</v>
+        <v>60.15625</v>
       </c>
       <c r="I11" s="23">
         <f t="shared" si="1"/>
@@ -57658,7 +57658,7 @@
       </c>
       <c r="G74" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B74,Station_Visual_Nodes!$J$2:$J$2000)+Q74,0)</f>
-        <v>1556</v>
+        <v>1564</v>
       </c>
       <c r="H74" s="23">
         <f t="shared" si="2"/>
@@ -57666,7 +57666,7 @@
       </c>
       <c r="I74" s="23">
         <f t="shared" si="3"/>
-        <v>54.027777777777771</v>
+        <v>54.30555555555555</v>
       </c>
       <c r="J74" s="2">
         <v>10.5</v>
@@ -57713,7 +57713,7 @@
       </c>
       <c r="G75" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B75,Station_Visual_Nodes!$J$2:$J$2000)+Q75,0)</f>
-        <v>1636</v>
+        <v>1652</v>
       </c>
       <c r="H75" s="23">
         <f t="shared" si="2"/>
@@ -57721,7 +57721,7 @@
       </c>
       <c r="I75" s="23">
         <f t="shared" si="3"/>
-        <v>56.805555555555557</v>
+        <v>57.361111111111107</v>
       </c>
       <c r="J75" s="2">
         <v>10.5</v>
@@ -57768,7 +57768,7 @@
       </c>
       <c r="G76" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B76,Station_Visual_Nodes!$J$2:$J$2000)+Q76,0)</f>
-        <v>1760</v>
+        <v>1750</v>
       </c>
       <c r="H76" s="23">
         <f t="shared" si="2"/>
@@ -57776,7 +57776,7 @@
       </c>
       <c r="I76" s="23">
         <f t="shared" si="3"/>
-        <v>61.111111111111114</v>
+        <v>60.763888888888886</v>
       </c>
       <c r="J76" s="2">
         <v>10.5</v>
@@ -57823,7 +57823,7 @@
       </c>
       <c r="G77" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B77,Station_Visual_Nodes!$J$2:$J$2000)+Q77,0)</f>
-        <v>1828</v>
+        <v>1820</v>
       </c>
       <c r="H77" s="23">
         <f t="shared" si="2"/>
@@ -57831,7 +57831,7 @@
       </c>
       <c r="I77" s="23">
         <f t="shared" si="3"/>
-        <v>63.472222222222221</v>
+        <v>63.194444444444443</v>
       </c>
       <c r="J77" s="2">
         <v>10.5</v>
@@ -57878,7 +57878,7 @@
       </c>
       <c r="G78" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B78,Station_Visual_Nodes!$J$2:$J$2000)+Q78,0)</f>
-        <v>1884</v>
+        <v>1892</v>
       </c>
       <c r="H78" s="23">
         <f t="shared" si="2"/>
@@ -57886,7 +57886,7 @@
       </c>
       <c r="I78" s="23">
         <f t="shared" si="3"/>
-        <v>65.416666666666671</v>
+        <v>65.694444444444443</v>
       </c>
       <c r="J78" s="2">
         <v>10.5</v>
@@ -58919,7 +58919,7 @@
       </c>
       <c r="F97" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B97,Station_Visual_Nodes!$I$2:$I$2000)+P97,0)</f>
-        <v>3064</v>
+        <v>3080</v>
       </c>
       <c r="G97" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B97,Station_Visual_Nodes!$J$2:$J$2000)+Q97,0)</f>
@@ -58927,7 +58927,7 @@
       </c>
       <c r="H97" s="23">
         <f t="shared" si="2"/>
-        <v>59.843749999999993</v>
+        <v>60.15625</v>
       </c>
       <c r="I97" s="23">
         <f t="shared" si="3"/>
@@ -58974,7 +58974,7 @@
       </c>
       <c r="F98" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B98,Station_Visual_Nodes!$I$2:$I$2000)+P98,0)</f>
-        <v>2908</v>
+        <v>2920</v>
       </c>
       <c r="G98" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B98,Station_Visual_Nodes!$J$2:$J$2000)+Q98,0)</f>
@@ -58982,7 +58982,7 @@
       </c>
       <c r="H98" s="23">
         <f t="shared" si="2"/>
-        <v>56.796875</v>
+        <v>57.03125</v>
       </c>
       <c r="I98" s="23">
         <f t="shared" si="3"/>
@@ -59029,7 +59029,7 @@
       </c>
       <c r="F99" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B99,Station_Visual_Nodes!$I$2:$I$2000)+P99,0)</f>
-        <v>2752</v>
+        <v>2760</v>
       </c>
       <c r="G99" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B99,Station_Visual_Nodes!$J$2:$J$2000)+Q99,0)</f>
@@ -59037,7 +59037,7 @@
       </c>
       <c r="H99" s="23">
         <f t="shared" si="2"/>
-        <v>53.75</v>
+        <v>53.90625</v>
       </c>
       <c r="I99" s="23">
         <f t="shared" si="3"/>
@@ -59084,7 +59084,7 @@
       </c>
       <c r="F100" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B100,Station_Visual_Nodes!$I$2:$I$2000)+P100,0)</f>
-        <v>2596</v>
+        <v>2600</v>
       </c>
       <c r="G100" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B100,Station_Visual_Nodes!$J$2:$J$2000)+Q100,0)</f>
@@ -59092,7 +59092,7 @@
       </c>
       <c r="H100" s="23">
         <f t="shared" si="2"/>
-        <v>50.703125000000007</v>
+        <v>50.78125</v>
       </c>
       <c r="I100" s="23">
         <f t="shared" si="3"/>
@@ -61173,7 +61173,7 @@
       </c>
       <c r="F138" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B138,Station_Visual_Nodes!$I$2:$I$2000)+P138,0)</f>
-        <v>3084</v>
+        <v>3080</v>
       </c>
       <c r="G138" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B138,Station_Visual_Nodes!$J$2:$J$2000)+Q138,0)</f>
@@ -61181,7 +61181,7 @@
       </c>
       <c r="H138" s="23">
         <f t="shared" si="4"/>
-        <v>60.234374999999993</v>
+        <v>60.15625</v>
       </c>
       <c r="I138" s="23">
         <f t="shared" si="5"/>
@@ -62552,7 +62552,7 @@
       </c>
       <c r="G163" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B163,Station_Visual_Nodes!$J$2:$J$2000)+Q163,0)</f>
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="H163" s="23">
         <f t="shared" si="4"/>
@@ -62560,7 +62560,7 @@
       </c>
       <c r="I163" s="23">
         <f t="shared" si="5"/>
-        <v>11.25</v>
+        <v>12.361111111111111</v>
       </c>
       <c r="J163" s="2">
         <v>10.5</v>
@@ -63538,7 +63538,7 @@
       </c>
       <c r="F181" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B181,Station_Visual_Nodes!$I$2:$I$2000)+P181,0)</f>
-        <v>2660</v>
+        <v>2666</v>
       </c>
       <c r="G181" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B181,Station_Visual_Nodes!$J$2:$J$2000)+Q181,0)</f>
@@ -63546,7 +63546,7 @@
       </c>
       <c r="H181" s="23">
         <f t="shared" si="4"/>
-        <v>51.953125</v>
+        <v>52.070312500000007</v>
       </c>
       <c r="I181" s="23">
         <f t="shared" si="5"/>
@@ -63593,7 +63593,7 @@
       </c>
       <c r="F182" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B182,Station_Visual_Nodes!$I$2:$I$2000)+P182,0)</f>
-        <v>2792</v>
+        <v>2804</v>
       </c>
       <c r="G182" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B182,Station_Visual_Nodes!$J$2:$J$2000)+Q182,0)</f>
@@ -63601,7 +63601,7 @@
       </c>
       <c r="H182" s="23">
         <f t="shared" si="4"/>
-        <v>54.53125</v>
+        <v>54.765624999999993</v>
       </c>
       <c r="I182" s="23">
         <f t="shared" si="5"/>
@@ -63648,7 +63648,7 @@
       </c>
       <c r="F183" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B183,Station_Visual_Nodes!$I$2:$I$2000)+P183,0)</f>
-        <v>2924</v>
+        <v>2942</v>
       </c>
       <c r="G183" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B183,Station_Visual_Nodes!$J$2:$J$2000)+Q183,0)</f>
@@ -63656,7 +63656,7 @@
       </c>
       <c r="H183" s="23">
         <f t="shared" si="4"/>
-        <v>57.109374999999993</v>
+        <v>57.4609375</v>
       </c>
       <c r="I183" s="23">
         <f t="shared" si="5"/>
@@ -63703,7 +63703,7 @@
       </c>
       <c r="F184" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B184,Station_Visual_Nodes!$I$2:$I$2000)+P184,0)</f>
-        <v>3056</v>
+        <v>3080</v>
       </c>
       <c r="G184" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B184,Station_Visual_Nodes!$J$2:$J$2000)+Q184,0)</f>
@@ -63711,7 +63711,7 @@
       </c>
       <c r="H184" s="23">
         <f t="shared" si="4"/>
-        <v>59.687500000000007</v>
+        <v>60.15625</v>
       </c>
       <c r="I184" s="23">
         <f t="shared" si="5"/>
@@ -63758,7 +63758,7 @@
       </c>
       <c r="F185" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B185,Station_Visual_Nodes!$I$2:$I$2000)+P185,0)</f>
-        <v>3188</v>
+        <v>3200</v>
       </c>
       <c r="G185" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B185,Station_Visual_Nodes!$J$2:$J$2000)+Q185,0)</f>
@@ -63766,7 +63766,7 @@
       </c>
       <c r="H185" s="23">
         <f t="shared" si="4"/>
-        <v>62.265625</v>
+        <v>62.5</v>
       </c>
       <c r="I185" s="23">
         <f t="shared" si="5"/>
@@ -64858,7 +64858,7 @@
       </c>
       <c r="F205" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B205,Station_Visual_Nodes!$I$2:$I$2000)+P205,0)</f>
-        <v>3078</v>
+        <v>3080</v>
       </c>
       <c r="G205" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B205,Station_Visual_Nodes!$J$2:$J$2000)+Q205,0)</f>
@@ -64866,7 +64866,7 @@
       </c>
       <c r="H205" s="23">
         <f t="shared" si="6"/>
-        <v>60.1171875</v>
+        <v>60.15625</v>
       </c>
       <c r="I205" s="23">
         <f t="shared" si="7"/>

--- a/data/master/yeoyuro_seoul_vector_map_coordinate_workbook.xlsx
+++ b/data/master/yeoyuro_seoul_vector_map_coordinate_workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\MyProject\yeoyuro_seoul_project\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8327742E-E5FD-42FC-A21A-3FD3B81E2F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78DF921-E95B-458E-BA29-6BEA4D13D436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7125" yWindow="1545" windowWidth="28800" windowHeight="15345" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22896,7 +22896,7 @@
         <v>1296</v>
       </c>
       <c r="J185" s="22">
-        <v>780</v>
+        <v>800</v>
       </c>
       <c r="K185" s="23">
         <f t="shared" si="4"/>
@@ -22904,7 +22904,7 @@
       </c>
       <c r="L185" s="23">
         <f t="shared" si="5"/>
-        <v>27.083333333333332</v>
+        <v>27.777777777777779</v>
       </c>
       <c r="M185" s="2">
         <v>10</v>
@@ -22950,7 +22950,7 @@
         <v>1296</v>
       </c>
       <c r="J186" s="22">
-        <v>884</v>
+        <v>916</v>
       </c>
       <c r="K186" s="23">
         <f t="shared" si="4"/>
@@ -22958,7 +22958,7 @@
       </c>
       <c r="L186" s="23">
         <f t="shared" si="5"/>
-        <v>30.694444444444446</v>
+        <v>31.805555555555554</v>
       </c>
       <c r="M186" s="2">
         <v>10</v>
@@ -48436,7 +48436,7 @@
       </c>
       <c r="G165" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B165,Station_Visual_Nodes!$J$2:$J$2000)+O165,0)</f>
-        <v>780</v>
+        <v>800</v>
       </c>
       <c r="H165" s="23">
         <f t="shared" si="4"/>
@@ -48444,7 +48444,7 @@
       </c>
       <c r="I165" s="23">
         <f t="shared" si="5"/>
-        <v>27.083333333333332</v>
+        <v>27.777777777777779</v>
       </c>
       <c r="J165" s="2">
         <v>24</v>
@@ -48485,7 +48485,7 @@
       </c>
       <c r="G166" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B166,Station_Visual_Nodes!$J$2:$J$2000)+O166,0)</f>
-        <v>884</v>
+        <v>916</v>
       </c>
       <c r="H166" s="23">
         <f t="shared" si="4"/>
@@ -48493,7 +48493,7 @@
       </c>
       <c r="I166" s="23">
         <f t="shared" si="5"/>
-        <v>30.694444444444446</v>
+        <v>31.805555555555554</v>
       </c>
       <c r="J166" s="2">
         <v>24</v>
@@ -62662,7 +62662,7 @@
       </c>
       <c r="G165" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B165,Station_Visual_Nodes!$J$2:$J$2000)+Q165,0)</f>
-        <v>780</v>
+        <v>800</v>
       </c>
       <c r="H165" s="23">
         <f t="shared" si="4"/>
@@ -62670,7 +62670,7 @@
       </c>
       <c r="I165" s="23">
         <f t="shared" si="5"/>
-        <v>27.083333333333332</v>
+        <v>27.777777777777779</v>
       </c>
       <c r="J165" s="2">
         <v>10.5</v>
@@ -62717,7 +62717,7 @@
       </c>
       <c r="G166" s="23">
         <f>ROUND(AVERAGEIF(Station_Visual_Nodes!$D$2:$D$2000,$B166,Station_Visual_Nodes!$J$2:$J$2000)+Q166,0)</f>
-        <v>884</v>
+        <v>916</v>
       </c>
       <c r="H166" s="23">
         <f t="shared" si="4"/>
@@ -62725,7 +62725,7 @@
       </c>
       <c r="I166" s="23">
         <f t="shared" si="5"/>
-        <v>30.694444444444446</v>
+        <v>31.805555555555554</v>
       </c>
       <c r="J166" s="2">
         <v>10.5</v>
